--- a/data/trans_orig/DCD-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2012</t>
+          <t>Población con dolor crónico discapacitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68832</t>
+          <t>67336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>48791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81537</t>
+          <t>80859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276269</t>
+          <t>275203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289346</t>
+          <t>288639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218413</t>
+          <t>219909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247442</t>
+          <t>247571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>501124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532898</t>
+          <t>533192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>60577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93579</t>
+          <t>94012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85655</t>
+          <t>85727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125713</t>
+          <t>126924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462061</t>
+          <t>461510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485751</t>
+          <t>485523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>430186</t>
+          <t>429753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462925</t>
+          <t>463188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903579</t>
+          <t>902368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>943637</t>
+          <t>943565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29611</t>
+          <t>27630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30959</t>
+          <t>31345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57191</t>
+          <t>57322</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46216</t>
+          <t>47087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76893</t>
+          <t>77274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294435</t>
+          <t>296416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313746</t>
+          <t>313771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283829</t>
+          <t>283698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310061</t>
+          <t>309675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>588173</t>
+          <t>587792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>618850</t>
+          <t>617979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41942</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>60784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91154</t>
+          <t>92754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85498</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123561</t>
+          <t>124780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>332040</t>
+          <t>332338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355019</t>
+          <t>355473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297797</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329112</t>
+          <t>328167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>639372</t>
+          <t>638153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>677435</t>
+          <t>677683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>19614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>40714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60408</t>
+          <t>58648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88352</t>
+          <t>87452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85200</t>
+          <t>83990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121786</t>
+          <t>120296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171724</t>
+          <t>171904</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193164</t>
+          <t>193004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131239</t>
+          <t>132139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159183</t>
+          <t>160943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310423</t>
+          <t>311913</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>347009</t>
+          <t>348219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41526</t>
+          <t>41818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>34443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59264</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>59488</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93994</t>
+          <t>92472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232455</t>
+          <t>232163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252981</t>
+          <t>254067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>220767</t>
+          <t>219548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246247</t>
+          <t>245588</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>460018</t>
+          <t>461540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492239</t>
+          <t>494524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54362</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88923</t>
+          <t>88288</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128253</t>
+          <t>126469</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125286</t>
+          <t>125399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170903</t>
+          <t>171458</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>608426</t>
+          <t>608318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>633082</t>
+          <t>632343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>565600</t>
+          <t>567384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>604930</t>
+          <t>605565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1185738</t>
+          <t>1185183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1231355</t>
+          <t>1231242</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30163</t>
+          <t>30798</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55750</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87712</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127727</t>
+          <t>127044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127798</t>
+          <t>128293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>172899</t>
+          <t>174309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>723348</t>
+          <t>723327</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>748935</t>
+          <t>748300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696126</t>
+          <t>696809</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>736141</t>
+          <t>737005</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1430052</t>
+          <t>1428642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1475153</t>
+          <t>1474658</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199449</t>
+          <t>198343</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>260328</t>
+          <t>256990</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>537033</t>
+          <t>537418</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>626371</t>
+          <t>624984</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>757863</t>
+          <t>753113</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>861259</t>
+          <t>862980</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3166451</t>
+          <t>3169789</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3227330</t>
+          <t>3228436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2931938</t>
+          <t>2933325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3021276</t>
+          <t>3020891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6123829</t>
+          <t>6122108</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6227225</t>
+          <t>6231975</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2016</t>
+          <t>Población con dolor crónico discapacitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48392</t>
+          <t>48736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78103</t>
+          <t>76686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>62654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94956</t>
+          <t>98428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265855</t>
+          <t>266405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283327</t>
+          <t>283536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210600</t>
+          <t>212017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>240311</t>
+          <t>239967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>487508</t>
+          <t>484036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519279</t>
+          <t>519810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>30700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27448</t>
+          <t>27189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>52166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45792</t>
+          <t>45091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75986</t>
+          <t>75455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>471750</t>
+          <t>471875</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489046</t>
+          <t>489470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470658</t>
+          <t>470918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495636</t>
+          <t>495895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>949673</t>
+          <t>950204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>979867</t>
+          <t>980568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25502</t>
+          <t>26012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>30873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>57159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>45125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75443</t>
+          <t>74639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293063</t>
+          <t>292553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308665</t>
+          <t>307910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280299</t>
+          <t>279150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305683</t>
+          <t>305436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>579431</t>
+          <t>580235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609408</t>
+          <t>609749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>23342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>46238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54758</t>
+          <t>53807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86041</t>
+          <t>86897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82577</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121274</t>
+          <t>122074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322744</t>
+          <t>323726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346482</t>
+          <t>346622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>301242</t>
+          <t>300386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>332525</t>
+          <t>333476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635973</t>
+          <t>635173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>674670</t>
+          <t>674099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48526</t>
+          <t>49153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>41029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69332</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183965</t>
+          <t>183582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200255</t>
+          <t>200735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170061</t>
+          <t>169434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191741</t>
+          <t>191452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360476</t>
+          <t>360451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388248</t>
+          <t>388779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49468</t>
+          <t>50154</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>41145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233624</t>
+          <t>234067</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251415</t>
+          <t>251292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223647</t>
+          <t>222961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246682</t>
+          <t>246999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463180</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>493506</t>
+          <t>495093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37741</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68312</t>
+          <t>66340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67912</t>
+          <t>67785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105628</t>
+          <t>106360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116872</t>
+          <t>115691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161664</t>
+          <t>165240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>588246</t>
+          <t>590218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>618817</t>
+          <t>619488</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>585666</t>
+          <t>584934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>623382</t>
+          <t>623509</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1186188</t>
+          <t>1182612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1230980</t>
+          <t>1232161</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>38939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68223</t>
+          <t>65559</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>75921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112838</t>
+          <t>114330</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>123121</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171837</t>
+          <t>167345</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>710360</t>
+          <t>713024</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>738774</t>
+          <t>739644</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>713329</t>
+          <t>711837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>751123</t>
+          <t>750246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1432913</t>
+          <t>1437405</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1481629</t>
+          <t>1484806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199191</t>
+          <t>199386</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>260919</t>
+          <t>259359</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>422039</t>
+          <t>425440</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>505227</t>
+          <t>510224</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>639330</t>
+          <t>638683</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>743382</t>
+          <t>741169</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3133431</t>
+          <t>3134991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3195159</t>
+          <t>3194964</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3039315</t>
+          <t>3034318</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3122503</t>
+          <t>3119102</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6195510</t>
+          <t>6197723</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6299562</t>
+          <t>6300209</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2023</t>
+          <t>Población con dolor crónico discapacitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20750</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>39883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>39679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58939</t>
+          <t>59159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63629</t>
+          <t>64076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92279</t>
+          <t>92329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271097</t>
+          <t>271560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290693</t>
+          <t>290607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230696</t>
+          <t>230476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249710</t>
+          <t>249956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>508798</t>
+          <t>508748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537448</t>
+          <t>537001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45576</t>
+          <t>45299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81651</t>
+          <t>76645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122785</t>
+          <t>125182</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156973</t>
+          <t>157692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174825</t>
+          <t>176516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227616</t>
+          <t>226913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436739</t>
+          <t>441745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472814</t>
+          <t>473091</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357996</t>
+          <t>357277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>392184</t>
+          <t>389787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>805743</t>
+          <t>806446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>858534</t>
+          <t>856843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37156</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60002</t>
+          <t>60139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>79187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105025</t>
+          <t>104090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121637</t>
+          <t>122610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156520</t>
+          <t>157803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256048</t>
+          <t>255911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278894</t>
+          <t>278404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244103</t>
+          <t>245038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270371</t>
+          <t>269941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>508658</t>
+          <t>507375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543541</t>
+          <t>542568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33740</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59130</t>
+          <t>60149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>62351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132243</t>
+          <t>132247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113065</t>
+          <t>107498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174810</t>
+          <t>177688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>253427</t>
+          <t>252408</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278817</t>
+          <t>278105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343475</t>
+          <t>343471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415278</t>
+          <t>413367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613464</t>
+          <t>610586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>675209</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20042</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56369</t>
+          <t>56418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40205</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>74418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153191</t>
+          <t>153292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165912</t>
+          <t>166211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>202361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238737</t>
+          <t>236855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364485</t>
+          <t>363103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>397316</t>
+          <t>395904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>41234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62269</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73642</t>
+          <t>73721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97307</t>
+          <t>96396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118580</t>
+          <t>120429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151647</t>
+          <t>151291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207367</t>
+          <t>208056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229460</t>
+          <t>228402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159749</t>
+          <t>160660</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183414</t>
+          <t>183335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>375045</t>
+          <t>375401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408112</t>
+          <t>406263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>82639</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119317</t>
+          <t>121256</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119074</t>
+          <t>109199</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>311461</t>
+          <t>310646</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>198142</t>
+          <t>221305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>394568</t>
+          <t>396811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>504962</t>
+          <t>503023</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>541767</t>
+          <t>541640</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>537804</t>
+          <t>538619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>730191</t>
+          <t>740066</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1078976</t>
+          <t>1076733</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1275402</t>
+          <t>1252239</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31474</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104097</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142608</t>
+          <t>142504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>180478</t>
+          <t>179870</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146512</t>
+          <t>147996</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283195</t>
+          <t>284381</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>824623</t>
+          <t>823813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>897246</t>
+          <t>896986</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>537253</t>
+          <t>537861</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>575123</t>
+          <t>575227</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1363257</t>
+          <t>1362071</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1499940</t>
+          <t>1498456</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>337616</t>
+          <t>336018</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>477084</t>
+          <t>476740</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>736624</t>
+          <t>722617</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>976182</t>
+          <t>975036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1154101</t>
+          <t>1138230</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1428993</t>
+          <t>1424504</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2982733</t>
+          <t>2983077</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3122201</t>
+          <t>3123799</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2736098</t>
+          <t>2737244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2975656</t>
+          <t>2989663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5743104</t>
+          <t>5747593</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6017996</t>
+          <t>6033867</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19535</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39674</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67336</t>
+          <t>68484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48791</t>
+          <t>48396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>80336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275203</t>
+          <t>275677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288639</t>
+          <t>289098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219909</t>
+          <t>218761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247571</t>
+          <t>247626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501124</t>
+          <t>501647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533192</t>
+          <t>533587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60577</t>
+          <t>59600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94012</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>86815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126924</t>
+          <t>125917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461510</t>
+          <t>463209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485523</t>
+          <t>485561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429753</t>
+          <t>430482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463188</t>
+          <t>464165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>902368</t>
+          <t>903375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>943565</t>
+          <t>942477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31345</t>
+          <t>30661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57322</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47087</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>77110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296416</t>
+          <t>296296</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313771</t>
+          <t>313056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283698</t>
+          <t>284257</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309675</t>
+          <t>310359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>587792</t>
+          <t>587956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617979</t>
+          <t>617740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>40237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60784</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>93784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85250</t>
+          <t>85095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124780</t>
+          <t>123936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>332338</t>
+          <t>333745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355473</t>
+          <t>354696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296197</t>
+          <t>295167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>328167</t>
+          <t>327959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>638153</t>
+          <t>638997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>677683</t>
+          <t>677838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19614</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58648</t>
+          <t>58707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87452</t>
+          <t>87722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>84235</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120296</t>
+          <t>120574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171904</t>
+          <t>171739</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193004</t>
+          <t>192826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132139</t>
+          <t>131869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160943</t>
+          <t>160884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>311913</t>
+          <t>311635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>348219</t>
+          <t>347974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,51%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41818</t>
+          <t>40414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34443</t>
+          <t>33651</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60483</t>
+          <t>59796</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59488</t>
+          <t>58669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92472</t>
+          <t>92571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232163</t>
+          <t>233567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254067</t>
+          <t>254340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219548</t>
+          <t>220235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245588</t>
+          <t>246380</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461540</t>
+          <t>461441</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494524</t>
+          <t>495343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54470</t>
+          <t>54923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88288</t>
+          <t>89101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126469</t>
+          <t>129047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>124789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171458</t>
+          <t>173351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>608318</t>
+          <t>607865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>632343</t>
+          <t>633051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>567384</t>
+          <t>564806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>605565</t>
+          <t>604752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1185183</t>
+          <t>1183290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1231242</t>
+          <t>1231852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55771</t>
+          <t>55127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86848</t>
+          <t>89771</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127044</t>
+          <t>128495</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128293</t>
+          <t>127051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>174309</t>
+          <t>174747</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>723327</t>
+          <t>723971</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>748300</t>
+          <t>749114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696809</t>
+          <t>695358</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>737005</t>
+          <t>734082</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1428642</t>
+          <t>1428204</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1474658</t>
+          <t>1475900</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198343</t>
+          <t>198146</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>256990</t>
+          <t>256925</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>537418</t>
+          <t>536814</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>624984</t>
+          <t>626754</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>753113</t>
+          <t>757979</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>862980</t>
+          <t>871047</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3169789</t>
+          <t>3169854</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3228436</t>
+          <t>3228633</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2933325</t>
+          <t>2931555</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3020891</t>
+          <t>3021495</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6122108</t>
+          <t>6114041</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6231975</t>
+          <t>6227109</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>27099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>48673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76686</t>
+          <t>77603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62654</t>
+          <t>63258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98428</t>
+          <t>98715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266405</t>
+          <t>266662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283536</t>
+          <t>283694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212017</t>
+          <t>211100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239967</t>
+          <t>240030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484036</t>
+          <t>483749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519810</t>
+          <t>519206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>32850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27189</t>
+          <t>27042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52166</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45091</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75455</t>
+          <t>75302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>471875</t>
+          <t>469725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489470</t>
+          <t>488636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470918</t>
+          <t>471806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495895</t>
+          <t>496042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950204</t>
+          <t>950357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>980568</t>
+          <t>979441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>25479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30873</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57159</t>
+          <t>57461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45125</t>
+          <t>44887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>74405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292553</t>
+          <t>293086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307910</t>
+          <t>308714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279150</t>
+          <t>278848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305436</t>
+          <t>306077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>580235</t>
+          <t>580469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609749</t>
+          <t>609987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>22475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>46034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53807</t>
+          <t>53693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86897</t>
+          <t>84629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83148</t>
+          <t>82700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122074</t>
+          <t>122231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>323726</t>
+          <t>323930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346622</t>
+          <t>347489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300386</t>
+          <t>302654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333476</t>
+          <t>333590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635173</t>
+          <t>635016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>674099</t>
+          <t>674547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27135</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49153</t>
+          <t>49477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>41317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>69116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183582</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200735</t>
+          <t>201017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169434</t>
+          <t>169110</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191452</t>
+          <t>191629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360451</t>
+          <t>360692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388779</t>
+          <t>388491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>26551</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50154</t>
+          <t>50084</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41145</t>
+          <t>43711</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70573</t>
+          <t>71928</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234067</t>
+          <t>233826</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251292</t>
+          <t>251449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222961</t>
+          <t>223031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246999</t>
+          <t>246564</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>465665</t>
+          <t>464310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495093</t>
+          <t>492527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66340</t>
+          <t>67389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67785</t>
+          <t>67961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106360</t>
+          <t>103015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115691</t>
+          <t>117161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165240</t>
+          <t>161316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>590218</t>
+          <t>589169</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619488</t>
+          <t>618228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584934</t>
+          <t>588279</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>623509</t>
+          <t>623333</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1182612</t>
+          <t>1186536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1232161</t>
+          <t>1230691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>38248</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65559</t>
+          <t>66202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75921</t>
+          <t>75363</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114330</t>
+          <t>113197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>121466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>167345</t>
+          <t>166735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>713024</t>
+          <t>712381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>739644</t>
+          <t>740335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>711837</t>
+          <t>712970</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>750246</t>
+          <t>750804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1437405</t>
+          <t>1438015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1484806</t>
+          <t>1483284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199386</t>
+          <t>201723</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>259359</t>
+          <t>258952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>425440</t>
+          <t>422673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>510224</t>
+          <t>503963</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>638683</t>
+          <t>642058</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>741169</t>
+          <t>743100</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3134991</t>
+          <t>3135398</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3194964</t>
+          <t>3192627</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3034318</t>
+          <t>3040579</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3119102</t>
+          <t>3121869</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6197723</t>
+          <t>6195792</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6300209</t>
+          <t>6296834</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39883</t>
+          <t>41183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>48572</t>
+          <t>54355</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59159</t>
+          <t>65680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>77627</t>
+          <t>84273</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64076</t>
+          <t>71168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92329</t>
+          <t>100294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>282388</t>
+          <t>288928</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271560</t>
+          <t>277662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290607</t>
+          <t>297643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>241063</t>
+          <t>261706</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230476</t>
+          <t>250381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249956</t>
+          <t>271422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>523450</t>
+          <t>550633</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>508748</t>
+          <t>534612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537001</t>
+          <t>563738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45299</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76645</t>
+          <t>81491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>140210</t>
+          <t>146076</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125182</t>
+          <t>129541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157692</t>
+          <t>165501</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>200165</t>
+          <t>207892</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176516</t>
+          <t>181849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226913</t>
+          <t>237771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>458436</t>
+          <t>468832</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441745</t>
+          <t>449156</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>473091</t>
+          <t>483568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>374759</t>
+          <t>400418</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357277</t>
+          <t>380993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>389787</t>
+          <t>416953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>833194</t>
+          <t>869249</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>806446</t>
+          <t>839370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>856843</t>
+          <t>895292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>47652</t>
+          <t>46709</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37646</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60139</t>
+          <t>58519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90498</t>
+          <t>92182</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79187</t>
+          <t>79768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104090</t>
+          <t>106324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>138149</t>
+          <t>138891</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122610</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157803</t>
+          <t>155606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>268398</t>
+          <t>269284</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>255911</t>
+          <t>257474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278404</t>
+          <t>279993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>258630</t>
+          <t>264199</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245038</t>
+          <t>250057</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269941</t>
+          <t>276613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>527029</t>
+          <t>533484</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507375</t>
+          <t>516769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>542568</t>
+          <t>550500</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45715</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34452</t>
+          <t>37341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>65720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>102073</t>
+          <t>112937</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62351</t>
+          <t>98452</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132247</t>
+          <t>131937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>147788</t>
+          <t>162266</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107498</t>
+          <t>139040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177688</t>
+          <t>184231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>266842</t>
+          <t>323816</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252408</t>
+          <t>307425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278105</t>
+          <t>335804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>373645</t>
+          <t>309024</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343471</t>
+          <t>290024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413367</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>640486</t>
+          <t>632841</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>610586</t>
+          <t>610876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>656067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42565</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>52323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>60762</t>
+          <t>63439</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>53509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74418</t>
+          <t>75037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160545</t>
+          <t>186422</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153292</t>
+          <t>178741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166211</t>
+          <t>192507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>216214</t>
+          <t>184721</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202361</t>
+          <t>176595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>236855</t>
+          <t>193035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>376759</t>
+          <t>371143</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>363103</t>
+          <t>359545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395904</t>
+          <t>381073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50161</t>
+          <t>49632</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>40356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61580</t>
+          <t>60113</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,27 +9123,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84634</t>
+          <t>86410</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73721</t>
+          <t>74391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96396</t>
+          <t>98914</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>134795</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120429</t>
+          <t>118629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151291</t>
+          <t>151255</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>219475</t>
+          <t>221075</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208056</t>
+          <t>210594</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228402</t>
+          <t>230351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,22 +9236,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>172422</t>
+          <t>177340</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160660</t>
+          <t>164836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183335</t>
+          <t>189359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>391897</t>
+          <t>398415</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>375401</t>
+          <t>383202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>406263</t>
+          <t>415828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>100908</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82639</t>
+          <t>96093</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121256</t>
+          <t>138236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>230688</t>
+          <t>280716</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109199</t>
+          <t>255089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310646</t>
+          <t>305079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>331596</t>
+          <t>397144</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221305</t>
+          <t>362343</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396811</t>
+          <t>432340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>523371</t>
+          <t>603259</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>503023</t>
+          <t>581451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>541640</t>
+          <t>623594</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>618577</t>
+          <t>491341</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>538619</t>
+          <t>466978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>740066</t>
+          <t>516968</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1141948</t>
+          <t>1094600</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1076733</t>
+          <t>1059404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1252239</t>
+          <t>1129401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>72402</t>
+          <t>81836</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31734</t>
+          <t>68512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104907</t>
+          <t>99404</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>160713</t>
+          <t>181036</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142504</t>
+          <t>162214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179870</t>
+          <t>201229</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>233115</t>
+          <t>262873</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147996</t>
+          <t>240332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>284381</t>
+          <t>291979</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>856318</t>
+          <t>716236</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>823813</t>
+          <t>698668</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>896986</t>
+          <t>729560</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>557018</t>
+          <t>650295</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>537861</t>
+          <t>630102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>575227</t>
+          <t>669117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1413337</t>
+          <t>1366530</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1362071</t>
+          <t>1337424</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1498456</t>
+          <t>1389071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>336018</t>
+          <t>418162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>476740</t>
+          <t>503157</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>899952</t>
+          <t>997910</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>722617</t>
+          <t>952398</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>975036</t>
+          <t>1048222</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1323997</t>
+          <t>1452821</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1138230</t>
+          <t>1385950</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1424504</t>
+          <t>1517258</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3035772</t>
+          <t>3077851</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2983077</t>
+          <t>3029605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3123799</t>
+          <t>3114600</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2812328</t>
+          <t>2739044</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2737244</t>
+          <t>2688732</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2989663</t>
+          <t>2784556</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5848100</t>
+          <t>5816895</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5747593</t>
+          <t>5752458</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6033867</t>
+          <t>5883766</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
